--- a/CO2xNxPhrag/Porewater/Sulfide/2026/Datasheets/2026May_LTREB_H2S_Datasheets.xlsx
+++ b/CO2xNxPhrag/Porewater/Sulfide/2026/Datasheets/2026May_LTREB_H2S_Datasheets.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sinet-my.sharepoint.com/personal/giessnerm_si_edu/Documents/Documents/GitHub/GCREW/CO2xN/Porewater/Sulfide/2026/Datasheets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sinet-my.sharepoint.com/personal/giessnerm_si_edu/Documents/Documents/GitHub/GCREW/CO2xNxPhrag/Porewater/Sulfide/2026/Datasheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{04B8FEBC-D623-4A8A-81A9-54A0B2E2DEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7F36F73-2952-46F3-A7E8-06416144AA5F}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{04B8FEBC-D623-4A8A-81A9-54A0B2E2DEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D98A8E87-6F3F-48E5-A136-EC0A1232EDF6}"/>
   <bookViews>
-    <workbookView xWindow="23025" yWindow="1995" windowWidth="15795" windowHeight="13485" firstSheet="3" activeTab="3" xr2:uid="{23FB6DB2-3641-4E78-A68E-113D11F8B05A}"/>
+    <workbookView xWindow="21150" yWindow="510" windowWidth="17805" windowHeight="14565" firstSheet="3" activeTab="7" xr2:uid="{23FB6DB2-3641-4E78-A68E-113D11F8B05A}"/>
   </bookViews>
   <sheets>
     <sheet name="STD 1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,9 @@
     <sheet name="Plate 4" sheetId="6" r:id="rId6"/>
     <sheet name="STD 3" sheetId="8" r:id="rId7"/>
     <sheet name="Plate 5" sheetId="7" r:id="rId8"/>
-    <sheet name="QAQC" sheetId="2" r:id="rId9"/>
+    <sheet name="Rerun 1" sheetId="10" r:id="rId9"/>
+    <sheet name="Rerun 2" sheetId="11" r:id="rId10"/>
+    <sheet name="QAQC" sheetId="2" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -44,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="151">
   <si>
     <t>A</t>
   </si>
@@ -425,6 +427,78 @@
   </si>
   <si>
     <t>Melanie</t>
+  </si>
+  <si>
+    <t>Ch11-5</t>
+  </si>
+  <si>
+    <t>462-10</t>
+  </si>
+  <si>
+    <t>Ch4-80</t>
+  </si>
+  <si>
+    <t>442-120</t>
+  </si>
+  <si>
+    <t>Ch4-40</t>
+  </si>
+  <si>
+    <t>P3-40 Dup</t>
+  </si>
+  <si>
+    <t>321-20</t>
+  </si>
+  <si>
+    <t>Ch8-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ch2-5 Spike</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P4-20 Spike</t>
+  </si>
+  <si>
+    <t>331-10</t>
+  </si>
+  <si>
+    <t>461-10 Dup</t>
+  </si>
+  <si>
+    <t>Ch2-5</t>
+  </si>
+  <si>
+    <t>461-10</t>
+  </si>
+  <si>
+    <t>453-10 x1 very dirty</t>
+  </si>
+  <si>
+    <t>323-20</t>
+  </si>
+  <si>
+    <t>323-80</t>
+  </si>
+  <si>
+    <t>613-80</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 331-10 Dup</t>
+  </si>
+  <si>
+    <t>633-10</t>
+  </si>
+  <si>
+    <t>323-10 Spike</t>
+  </si>
+  <si>
+    <t>633-40</t>
+  </si>
+  <si>
+    <t>461-10 Spike</t>
+  </si>
+  <si>
+    <t>323-10</t>
   </si>
 </sst>
 </file>
@@ -551,6 +625,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1308,6 +1386,767 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99EDEB4D-1CF5-4D87-A178-32C91E3C5434}">
+  <dimension ref="A1:N23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="3"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="3"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="N5" s="3"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="N6" s="3"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N7" s="3"/>
+    </row>
+    <row r="8" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2">
+        <v>3</v>
+      </c>
+      <c r="E11" s="2">
+        <v>4</v>
+      </c>
+      <c r="F11" s="2">
+        <v>5</v>
+      </c>
+      <c r="G11" s="2">
+        <v>6</v>
+      </c>
+      <c r="H11" s="2">
+        <v>7</v>
+      </c>
+      <c r="I11" s="2">
+        <v>8</v>
+      </c>
+      <c r="J11" s="2">
+        <v>9</v>
+      </c>
+      <c r="K11" s="2">
+        <v>10</v>
+      </c>
+      <c r="L11" s="2">
+        <v>11</v>
+      </c>
+      <c r="M11" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="4">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4">
+        <v>100</v>
+      </c>
+      <c r="F12" s="4">
+        <v>100</v>
+      </c>
+      <c r="G12" s="4">
+        <v>100</v>
+      </c>
+      <c r="H12" s="4">
+        <v>100</v>
+      </c>
+      <c r="I12" s="4">
+        <v>100</v>
+      </c>
+      <c r="J12" s="4">
+        <v>100</v>
+      </c>
+      <c r="K12" s="4">
+        <v>100</v>
+      </c>
+      <c r="L12" s="4">
+        <v>100</v>
+      </c>
+      <c r="M12" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="4">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4">
+        <v>100</v>
+      </c>
+      <c r="F13" s="4">
+        <v>100</v>
+      </c>
+      <c r="G13" s="4">
+        <v>100</v>
+      </c>
+      <c r="H13" s="4">
+        <v>1</v>
+      </c>
+      <c r="I13" s="4">
+        <v>1</v>
+      </c>
+      <c r="J13" s="4">
+        <v>1</v>
+      </c>
+      <c r="K13" s="4">
+        <v>100</v>
+      </c>
+      <c r="L13" s="4">
+        <v>100</v>
+      </c>
+      <c r="M13" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="4">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4">
+        <v>1</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4">
+        <v>100</v>
+      </c>
+      <c r="F14" s="4">
+        <v>100</v>
+      </c>
+      <c r="G14" s="4">
+        <v>100</v>
+      </c>
+      <c r="H14" s="4">
+        <v>100</v>
+      </c>
+      <c r="I14" s="4">
+        <v>100</v>
+      </c>
+      <c r="J14" s="4">
+        <v>100</v>
+      </c>
+      <c r="K14" s="4">
+        <v>100</v>
+      </c>
+      <c r="L14" s="4">
+        <v>100</v>
+      </c>
+      <c r="M14" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="4">
+        <v>1</v>
+      </c>
+      <c r="C15" s="4">
+        <v>1</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4">
+        <v>100</v>
+      </c>
+      <c r="F15" s="4">
+        <v>100</v>
+      </c>
+      <c r="G15" s="4">
+        <v>100</v>
+      </c>
+      <c r="H15" s="4">
+        <v>1</v>
+      </c>
+      <c r="I15" s="4">
+        <v>1</v>
+      </c>
+      <c r="J15" s="4">
+        <v>1</v>
+      </c>
+      <c r="K15" s="4">
+        <v>100</v>
+      </c>
+      <c r="L15" s="4">
+        <v>100</v>
+      </c>
+      <c r="M15" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="4">
+        <v>1</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4">
+        <v>100</v>
+      </c>
+      <c r="F16" s="4">
+        <v>100</v>
+      </c>
+      <c r="G16" s="4">
+        <v>100</v>
+      </c>
+      <c r="H16" s="4">
+        <v>100</v>
+      </c>
+      <c r="I16" s="4">
+        <v>100</v>
+      </c>
+      <c r="J16" s="4">
+        <v>100</v>
+      </c>
+      <c r="K16" s="4">
+        <v>100</v>
+      </c>
+      <c r="L16" s="4">
+        <v>100</v>
+      </c>
+      <c r="M16" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="4">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4">
+        <v>100</v>
+      </c>
+      <c r="F17" s="4">
+        <v>100</v>
+      </c>
+      <c r="G17" s="4">
+        <v>100</v>
+      </c>
+      <c r="H17" s="4">
+        <v>100</v>
+      </c>
+      <c r="I17" s="4">
+        <v>100</v>
+      </c>
+      <c r="J17" s="4">
+        <v>100</v>
+      </c>
+      <c r="K17" s="4">
+        <v>1</v>
+      </c>
+      <c r="L17" s="4">
+        <v>1</v>
+      </c>
+      <c r="M17" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="4">
+        <v>1</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4">
+        <v>100</v>
+      </c>
+      <c r="F18" s="4">
+        <v>100</v>
+      </c>
+      <c r="G18" s="4">
+        <v>100</v>
+      </c>
+      <c r="H18" s="4">
+        <v>100</v>
+      </c>
+      <c r="I18" s="4">
+        <v>100</v>
+      </c>
+      <c r="J18" s="4">
+        <v>100</v>
+      </c>
+      <c r="K18" s="4">
+        <v>100</v>
+      </c>
+      <c r="L18" s="4">
+        <v>100</v>
+      </c>
+      <c r="M18" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="4">
+        <v>100</v>
+      </c>
+      <c r="C19" s="4">
+        <v>100</v>
+      </c>
+      <c r="D19" s="4">
+        <v>100</v>
+      </c>
+      <c r="E19" s="4">
+        <v>100</v>
+      </c>
+      <c r="F19" s="4">
+        <v>100</v>
+      </c>
+      <c r="G19" s="4">
+        <v>100</v>
+      </c>
+      <c r="H19" s="4">
+        <v>100</v>
+      </c>
+      <c r="I19" s="4">
+        <v>100</v>
+      </c>
+      <c r="J19" s="4">
+        <v>100</v>
+      </c>
+      <c r="K19" s="4">
+        <v>1</v>
+      </c>
+      <c r="L19" s="4">
+        <v>1</v>
+      </c>
+      <c r="M19" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>141</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74720A33-EA02-4F3B-99BC-21807D7702E9}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.28515625" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="7">
+        <v>46163</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1891C68-457C-474D-B98D-A8DDB35A9BFE}">
   <dimension ref="A1:N22"/>
@@ -5807,13 +6646,13 @@
         <v>50</v>
       </c>
       <c r="K14" s="4">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="L14" s="4">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="M14" s="4">
-        <v>50</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -5971,13 +6810,13 @@
         <v>50</v>
       </c>
       <c r="K18" s="4">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="L18" s="4">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="M18" s="4">
-        <v>50</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -6034,39 +6873,766 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74720A33-EA02-4F3B-99BC-21807D7702E9}">
-  <dimension ref="A1:B3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB37C29B-D061-4F55-A06C-EDC6A3254A18}">
+  <dimension ref="A1:N23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13.28515625" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="7">
-        <v>46163</v>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="N3" s="3"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="N4" s="3"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="N5" s="3"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="N6" s="3"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N7" s="3"/>
+    </row>
+    <row r="8" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2">
+        <v>3</v>
+      </c>
+      <c r="E11" s="2">
+        <v>4</v>
+      </c>
+      <c r="F11" s="2">
+        <v>5</v>
+      </c>
+      <c r="G11" s="2">
+        <v>6</v>
+      </c>
+      <c r="H11" s="2">
+        <v>7</v>
+      </c>
+      <c r="I11" s="2">
+        <v>8</v>
+      </c>
+      <c r="J11" s="2">
+        <v>9</v>
+      </c>
+      <c r="K11" s="2">
+        <v>10</v>
+      </c>
+      <c r="L11" s="2">
+        <v>11</v>
+      </c>
+      <c r="M11" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="4">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4">
+        <v>1</v>
+      </c>
+      <c r="F12" s="4">
+        <v>1</v>
+      </c>
+      <c r="G12" s="4">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4">
+        <v>1</v>
+      </c>
+      <c r="I12" s="4">
+        <v>1</v>
+      </c>
+      <c r="J12" s="4">
+        <v>1</v>
+      </c>
+      <c r="K12" s="4">
+        <v>1</v>
+      </c>
+      <c r="L12" s="4">
+        <v>1</v>
+      </c>
+      <c r="M12" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="4">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4">
+        <v>100</v>
+      </c>
+      <c r="F13" s="4">
+        <v>100</v>
+      </c>
+      <c r="G13" s="4">
+        <v>100</v>
+      </c>
+      <c r="H13" s="4">
+        <v>1</v>
+      </c>
+      <c r="I13" s="4">
+        <v>1</v>
+      </c>
+      <c r="J13" s="4">
+        <v>1</v>
+      </c>
+      <c r="K13" s="4">
+        <v>100</v>
+      </c>
+      <c r="L13" s="4">
+        <v>100</v>
+      </c>
+      <c r="M13" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="4">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4">
+        <v>1</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4">
+        <v>100</v>
+      </c>
+      <c r="F14" s="4">
+        <v>100</v>
+      </c>
+      <c r="G14" s="4">
+        <v>100</v>
+      </c>
+      <c r="H14" s="4">
+        <v>1</v>
+      </c>
+      <c r="I14" s="4">
+        <v>1</v>
+      </c>
+      <c r="J14" s="4">
+        <v>1</v>
+      </c>
+      <c r="K14" s="4">
+        <v>100</v>
+      </c>
+      <c r="L14" s="4">
+        <v>100</v>
+      </c>
+      <c r="M14" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="4">
+        <v>1</v>
+      </c>
+      <c r="C15" s="4">
+        <v>1</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4">
+        <v>50</v>
+      </c>
+      <c r="F15" s="4">
+        <v>50</v>
+      </c>
+      <c r="G15" s="4">
+        <v>50</v>
+      </c>
+      <c r="H15" s="4">
+        <v>1</v>
+      </c>
+      <c r="I15" s="4">
+        <v>1</v>
+      </c>
+      <c r="J15" s="4">
+        <v>1</v>
+      </c>
+      <c r="K15" s="4">
+        <v>1</v>
+      </c>
+      <c r="L15" s="4">
+        <v>1</v>
+      </c>
+      <c r="M15" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="4">
+        <v>1</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4">
+        <v>1</v>
+      </c>
+      <c r="F16" s="4">
+        <v>1</v>
+      </c>
+      <c r="G16" s="4">
+        <v>1</v>
+      </c>
+      <c r="H16" s="4">
+        <v>1</v>
+      </c>
+      <c r="I16" s="4">
+        <v>1</v>
+      </c>
+      <c r="J16" s="4">
+        <v>1</v>
+      </c>
+      <c r="K16" s="4">
+        <v>1</v>
+      </c>
+      <c r="L16" s="4">
+        <v>1</v>
+      </c>
+      <c r="M16" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="4">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4">
+        <v>50</v>
+      </c>
+      <c r="F17" s="4">
+        <v>50</v>
+      </c>
+      <c r="G17" s="4">
+        <v>50</v>
+      </c>
+      <c r="H17" s="4">
+        <v>1</v>
+      </c>
+      <c r="I17" s="4">
+        <v>1</v>
+      </c>
+      <c r="J17" s="4">
+        <v>1</v>
+      </c>
+      <c r="K17" s="4">
+        <v>1</v>
+      </c>
+      <c r="L17" s="4">
+        <v>1</v>
+      </c>
+      <c r="M17" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="4">
+        <v>1</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4">
+        <v>50</v>
+      </c>
+      <c r="F18" s="4">
+        <v>50</v>
+      </c>
+      <c r="G18" s="4">
+        <v>50</v>
+      </c>
+      <c r="H18" s="4">
+        <v>1</v>
+      </c>
+      <c r="I18" s="4">
+        <v>1</v>
+      </c>
+      <c r="J18" s="4">
+        <v>1</v>
+      </c>
+      <c r="K18" s="4">
+        <v>100</v>
+      </c>
+      <c r="L18" s="4">
+        <v>100</v>
+      </c>
+      <c r="M18" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="4">
+        <v>1</v>
+      </c>
+      <c r="C19" s="4">
+        <v>1</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1</v>
+      </c>
+      <c r="E19" s="4">
+        <v>50</v>
+      </c>
+      <c r="F19" s="4">
+        <v>50</v>
+      </c>
+      <c r="G19" s="4">
+        <v>50</v>
+      </c>
+      <c r="H19" s="4">
+        <v>1</v>
+      </c>
+      <c r="I19" s="4">
+        <v>1</v>
+      </c>
+      <c r="J19" s="4">
+        <v>1</v>
+      </c>
+      <c r="K19" s="4">
+        <v>1</v>
+      </c>
+      <c r="L19" s="4">
+        <v>1</v>
+      </c>
+      <c r="M19" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>